--- a/artfynd/A 41874-2026 artfynd.xlsx
+++ b/artfynd/A 41874-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6950707</v>
+        <v>137493639</v>
       </c>
       <c r="B2" t="n">
-        <v>99754</v>
+        <v>75417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222295</v>
+        <v>94</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Puderfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Arthonia cinereopruinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>Schaer.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N. Kvisslehult 140 m VNV, Ög</t>
+          <t>Lillån, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504984</v>
+        <v>504876</v>
       </c>
       <c r="R2" t="n">
-        <v>6450757</v>
+        <v>6450671</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-08-10</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-08-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,24 +762,131 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Frisk gräsmark i skogsbryn</t>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Ek</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörgen Josefsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörgen Josefsson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137493639</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6950707</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99754</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222295</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vårstarr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carex caryophyllea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Latourr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>N. Kvisslehult 140 m VNV, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>504984</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6450757</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Boxholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åsbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2013-08-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2013-08-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Frisk gräsmark i skogsbryn</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jörgen Josefsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jörgen Josefsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6950707</t>
         </is>
@@ -788,6 +895,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41874-2026 artfynd.xlsx
+++ b/artfynd/A 41874-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137493639</v>
       </c>
       <c r="B2" t="n">
-        <v>75417</v>
+        <v>75421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
